--- a/erp-server/erp-server-file/src/main/resources/excel/fms/assetDisposal.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/fms/assetDisposal.xlsx
@@ -1070,122 +1070,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="D1:S2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="15.75" customWidth="1"/>
-    <col min="6" max="7" width="10.125" customWidth="1"/>
-    <col min="8" max="8" width="8.625" customWidth="1"/>
-    <col min="9" max="11" width="16.125" customWidth="1"/>
-    <col min="12" max="12" width="17.125" customWidth="1"/>
-    <col min="13" max="13" width="20.375" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="14.875" customWidth="1"/>
-    <col min="17" max="17" width="12.25" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="3" max="4" width="10.125" customWidth="1"/>
+    <col min="5" max="5" width="8.625" customWidth="1"/>
+    <col min="6" max="8" width="16.125" customWidth="1"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="10" max="10" width="20.375" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="14.875" customWidth="1"/>
+    <col min="14" max="14" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:19">
-      <c r="D1" s="1" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="4:19">
+    <row r="2" spans="1:16">
+      <c r="A2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="D2" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="3" t="s">
         <v>31</v>
       </c>
     </row>
